--- a/artfynd/A 15856-2026 artfynd.xlsx
+++ b/artfynd/A 15856-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>188140</v>
+        <v>101084562</v>
       </c>
       <c r="B2" t="n">
-        <v>95737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,16 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Farsbo ONO, 200 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522203.806162721</v>
+        <v>522204</v>
       </c>
       <c r="R2" t="n">
-        <v>6443074.973479222</v>
+        <v>6443075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,113 +744,107 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>E-Lin-0234</t>
+          <t>Arkiv-E-Lin-0046</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-06-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1976-01-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Jag gick inte in i skogsmarken öster om diket. 88C</t>
+          <t>Erik Moberger</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>E-län Floraväktarna</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janne Andersson</t>
+          <t>Via Sofia Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85568712</v>
+        <v>99634451</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Farsbo, 65 m NO vägskälet, Ög</t>
+          <t>500 m öst Stora Farsbo, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522223.8926146959</v>
+        <v>522399</v>
       </c>
       <c r="R3" t="n">
-        <v>6442889.189116011</v>
+        <v>6442971</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,23 +895,243 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>örtrik vägslänt</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anders Tennlind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Tennlind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99634452</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>500 m öst Stora Farsbo, Linköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522399</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6442971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Tennlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Tennlind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>85568712</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Farsbo, 65 m NO vägskälet, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522224</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6442889</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>örtrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Anders Svenson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Anders Svenson, Tommy Nilsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15856-2026 artfynd.xlsx
+++ b/artfynd/A 15856-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101084562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99634451</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99634452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85568712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>